--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486669_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486669_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2522</v>
+        <v>4.0282</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1884</v>
+        <v>2.6817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0639</v>
+        <v>1.3465</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9636</v>
+        <v>1.587</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0631</v>
+        <v>-0.572</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09950000000000001</v>
+        <v>2.159</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5711</v>
+        <v>2.2016</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4084</v>
+        <v>1.0147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1628</v>
+        <v>1.1869</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6075</v>
+        <v>-0.6146</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3453</v>
+        <v>-1.5867</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2623</v>
+        <v>0.972</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6861</v>
+        <v>1.0204</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8956</v>
+        <v>1.2684</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2095</v>
+        <v>-0.248</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.1698</v>
+        <v>1.2277</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.3129</v>
+        <v>1.1424</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8568</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4395</v>
+        <v>2.8002</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4406</v>
+        <v>2.6371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9989</v>
+        <v>0.1632</v>
       </c>
       <c r="G3" t="n">
-        <v>1.587</v>
+        <v>2.9636</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.572</v>
+        <v>3.0631</v>
       </c>
       <c r="I3" t="n">
-        <v>2.159</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2016</v>
+        <v>3.5711</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0147</v>
+        <v>3.4084</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1869</v>
+        <v>0.1628</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6146</v>
+        <v>-0.6075</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5867</v>
+        <v>-0.3453</v>
       </c>
       <c r="O3" t="n">
-        <v>0.972</v>
+        <v>-0.2623</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5683</v>
+        <v>1.2341</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0273</v>
+        <v>1.3442</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5956</v>
+        <v>-0.1101</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2277</v>
+        <v>-2.1698</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1424</v>
+        <v>-1.3129</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0852</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2925</v>
+        <v>0.275</v>
       </c>
       <c r="E4" t="n">
-        <v>3.045</v>
+        <v>-0.773</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7525</v>
+        <v>1.048</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3993</v>
+        <v>0.4198</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5658</v>
+        <v>-0.1725</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1665</v>
+        <v>0.5923</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9946</v>
+        <v>0.1442</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1589</v>
+        <v>0.1035</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8357</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3939</v>
+        <v>0.2756</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7247</v>
+        <v>-0.2759</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6692</v>
+        <v>0.5516</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4987</v>
+        <v>-0.1448</v>
       </c>
       <c r="T4" t="n">
-        <v>2.344</v>
+        <v>0.0482</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1547</v>
+        <v>-0.193</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6069</v>
+        <v>0.2718</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1302</v>
+        <v>0.82</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5233</v>
+        <v>-0.5482</v>
       </c>
       <c r="G5" t="n">
         <v>0.4266</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3421</v>
+        <v>0.007</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6343</v>
+        <v>0.324</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2922</v>
+        <v>-0.3171</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5133</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1219</v>
+        <v>0.1797</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8764</v>
+        <v>1.9074</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9983</v>
+        <v>-1.7277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4198</v>
+        <v>-0.3993</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1725</v>
+        <v>-1.5658</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5923</v>
+        <v>1.1665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1442</v>
+        <v>1.9946</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1035</v>
+        <v>0.1589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>1.8357</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2756</v>
+        <v>-2.3939</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2759</v>
+        <v>-1.7247</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5516</v>
+        <v>-0.6692</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2979</v>
+        <v>1.3859</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0552</v>
+        <v>1.2064</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2427</v>
+        <v>0.1795</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3388</v>
+        <v>-0.2146</v>
       </c>
       <c r="E7" t="n">
         <v>0.5677</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9065</v>
+        <v>-0.7823</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2285</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3034</v>
+        <v>-0.1792</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0318</v>
+        <v>-0.2789</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4957</v>
+        <v>1.323</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5275</v>
+        <v>-1.602</v>
       </c>
       <c r="G8" t="n">
         <v>0.7436</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>0.116</v>
+        <v>0.8689</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1104</v>
+        <v>0.717</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2264</v>
+        <v>0.1519</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0845</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARRO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7322</v>
+        <v>-1.227</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1918</v>
+        <v>0.828</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5404</v>
+        <v>-2.055</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2023</v>
+        <v>-3.2103</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8346</v>
+        <v>-2.0552</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3676</v>
+        <v>-1.1551</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5987</v>
+        <v>-0.0574</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7523</v>
+        <v>0.7043</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1536</v>
+        <v>-0.7617</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.801</v>
+        <v>-3.1529</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.587</v>
+        <v>-2.7595</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.214</v>
+        <v>-0.3934</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6125</v>
+        <v>0.462</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1107</v>
+        <v>0.3374</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7232</v>
+        <v>0.1245</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5286</v>
+        <v>0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8142</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>D. GARCIA NAVARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7616</v>
+        <v>-2.0965</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0243</v>
+        <v>0.0151</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7374</v>
+        <v>-2.1115</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.499</v>
+        <v>-2.2023</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2616</v>
+        <v>-0.8346</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2374</v>
+        <v>-1.3676</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.305</v>
+        <v>0.5987</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2218</v>
+        <v>0.7523</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.1536</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1941</v>
+        <v>-2.801</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4834</v>
+        <v>-1.587</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2893</v>
+        <v>-1.214</v>
       </c>
       <c r="P10" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9731</v>
+        <v>0.2482</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8679</v>
+        <v>0.0961</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1051</v>
+        <v>0.1521</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2703</v>
+        <v>-0.5286</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6138</v>
+        <v>-0.8142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4391</v>
+        <v>-3.028</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3097</v>
+        <v>-1.2062</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1294</v>
+        <v>-1.8217</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2103</v>
+        <v>-1.5442</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0552</v>
+        <v>0.2756</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1551</v>
+        <v>-1.8198</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0574</v>
+        <v>1.7398</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7043</v>
+        <v>2.3456</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7617</v>
+        <v>-0.6058</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1529</v>
+        <v>-3.284</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.7595</v>
+        <v>-2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3934</v>
+        <v>-1.214</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5792</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7502</v>
+        <v>0.0688</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8002</v>
+        <v>0.3443</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05</v>
+        <v>-0.2754</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9421</v>
+        <v>0.5712</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5133</v>
+        <v>0.5712</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6485</v>
+        <v>-3.3626</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8268</v>
+        <v>-1.5756</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8217</v>
+        <v>-1.787</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5442</v>
+        <v>-2.499</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2756</v>
+        <v>-2.2616</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8198</v>
+        <v>-0.2374</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7398</v>
+        <v>-0.305</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3456</v>
+        <v>0.2218</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6058</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.284</v>
+        <v>-2.1941</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.07</v>
+        <v>-2.4834</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.214</v>
+        <v>0.2893</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5517</v>
+        <v>1.3721</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2763</v>
+        <v>1.3166</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2754</v>
+        <v>0.0555</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5712</v>
+        <v>-1.2703</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5712</v>
+        <v>-0.6565</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2479</v>
+        <v>-3.8343</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8095</v>
+        <v>-0.3958</v>
       </c>
       <c r="F13" t="n">
         <v>-3.4384</v>
@@ -1468,10 +1468,10 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4137</v>
+        <v>0.8274</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.2408</v>
       </c>
       <c r="U13" t="n">
         <v>-0.4135</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.486899999999999</v>
+        <v>-6.486999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8291</v>
+        <v>6.829399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.316</v>
+        <v>-13.3161</v>
       </c>
       <c r="G14" t="n">
         <v>-4.2731</v>
@@ -1522,7 +1522,7 @@
         <v>10.4251</v>
       </c>
       <c r="K14" t="n">
-        <v>7.938099999999999</v>
+        <v>7.9381</v>
       </c>
       <c r="L14" t="n">
         <v>2.4874</v>
@@ -1534,10 +1534,10 @@
         <v>-14.8336</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1352</v>
+        <v>0.1351999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9653000000000004</v>
+        <v>0.9653000000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.5156</v>
@@ -1546,19 +1546,19 @@
         <v>14.4808</v>
       </c>
       <c r="S14" t="n">
-        <v>7.1707</v>
+        <v>7.170800000000001</v>
       </c>
       <c r="T14" t="n">
         <v>8.132999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9625000000000001</v>
+        <v>-0.9625</v>
       </c>
       <c r="V14" t="n">
         <v>-10.3501</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7861</v>
+        <v>1.786100000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-12.1362</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.2987</v>
+        <v>8.265599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3703</v>
+        <v>6.6463</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9284</v>
+        <v>1.6194</v>
       </c>
       <c r="G15" t="n">
         <v>4.0799</v>
@@ -1624,13 +1624,13 @@
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8333</v>
+        <v>-0.1997</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1303</v>
+        <v>0.4064</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.297</v>
+        <v>-0.6061</v>
       </c>
       <c r="V15" t="n">
         <v>3.227</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.145</v>
+        <v>1.5749</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7599</v>
+        <v>2.6315</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3851</v>
+        <v>-1.0566</v>
       </c>
       <c r="G16" t="n">
-        <v>2.712</v>
+        <v>1.1357</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5034</v>
+        <v>1.1447</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2086</v>
+        <v>-0.0091</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6581</v>
+        <v>2.6066</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7456</v>
+        <v>2.1114</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9125</v>
+        <v>0.4952</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-1.4709</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2422</v>
+        <v>-0.9667</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2961</v>
+        <v>-0.5042</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6494</v>
+        <v>-1.8617</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0406</v>
+        <v>-0.1521</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3912</v>
+        <v>-1.7095</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3282</v>
+        <v>1.1424</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0426</v>
+        <v>1.1424</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1805</v>
+        <v>1.5577</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4246</v>
+        <v>1.2085</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2441</v>
+        <v>0.3492</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1357</v>
+        <v>2.712</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1447</v>
+        <v>0.5034</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0091</v>
+        <v>2.2086</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6066</v>
+        <v>3.6581</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1114</v>
+        <v>1.7456</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4952</v>
+        <v>1.9125</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4709</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9667</v>
+        <v>-1.2422</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5042</v>
+        <v>0.2961</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1585</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2561</v>
+        <v>0.0621</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.359</v>
+        <v>0.4892</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8971</v>
+        <v>-0.4271</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1424</v>
+        <v>0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1424</v>
+        <v>-0.0426</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>G. CAMPOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5583</v>
+        <v>0.8989</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4255</v>
+        <v>2.0856</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1328</v>
+        <v>-1.1867</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8693</v>
+        <v>-1.7593</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5167</v>
+        <v>0.5171</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3526</v>
+        <v>-2.2765</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8017</v>
+        <v>-0.6828</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0692</v>
+        <v>0.6555</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7325</v>
+        <v>-1.3383</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9324</v>
+        <v>-1.0766</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5525</v>
+        <v>-0.1384</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3799</v>
+        <v>-0.9382</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1638</v>
+        <v>-1.0481</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0279</v>
+        <v>0.0274</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1359</v>
+        <v>-1.0755</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1698</v>
+        <v>2.741</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5133</v>
+        <v>2.741</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRIGUEZ</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3859</v>
+        <v>0.6121</v>
       </c>
       <c r="E19" t="n">
-        <v>1.672</v>
+        <v>0.529</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.286</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7593</v>
+        <v>1.8693</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5171</v>
+        <v>1.5167</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2765</v>
+        <v>0.3526</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6828</v>
+        <v>2.8017</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6555</v>
+        <v>2.0692</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3383</v>
+        <v>0.7325</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0766</v>
+        <v>-0.9324</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1384</v>
+        <v>-0.5525</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9382</v>
+        <v>-0.3799</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9654</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5611</v>
+        <v>-1.1101</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3863</v>
+        <v>0.0755</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1748</v>
+        <v>-1.1856</v>
       </c>
       <c r="V19" t="n">
-        <v>2.741</v>
+        <v>2.1698</v>
       </c>
       <c r="W19" t="n">
-        <v>2.741</v>
+        <v>1.5133</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2998</v>
+        <v>0.0119</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5790999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2793</v>
+        <v>0.591</v>
       </c>
       <c r="G20" t="n">
         <v>-1.283</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5462</v>
+        <v>-0.2345</v>
       </c>
       <c r="T20" t="n">
         <v>0.3032</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8494</v>
+        <v>-0.5377</v>
       </c>
       <c r="V20" t="n">
         <v>0.3709</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4382</v>
+        <v>-0.5804</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0347</v>
+        <v>1.6553</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4729</v>
+        <v>-2.2357</v>
       </c>
       <c r="G21" t="n">
         <v>1.8042</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0646</v>
+        <v>-0.2068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7174</v>
+        <v>-0.0968</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3472</v>
+        <v>-0.11</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5985</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5655</v>
+        <v>-1.2732</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0758</v>
+        <v>0.4882</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4898</v>
+        <v>-1.7613</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6829</v>
+        <v>0.1872</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4138</v>
+        <v>1.8963</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.269</v>
+        <v>-1.7091</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.0782</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2.7247</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6465</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6829</v>
+        <v>-1.891</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4138</v>
+        <v>-0.8285</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.269</v>
+        <v>-1.0626</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1104</v>
+        <v>-1.186</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1104</v>
+        <v>-0.2072</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.9788</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2703</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2165</v>
+        <v>-1.5655</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1324</v>
+        <v>-1.0758</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0841</v>
+        <v>-0.4898</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1872</v>
+        <v>-0.6829</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8963</v>
+        <v>-0.4138</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7091</v>
+        <v>-0.269</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0782</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7247</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6465</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.891</v>
+        <v>-0.6829</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8285</v>
+        <v>-0.4138</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0626</v>
+        <v>-0.269</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5446</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1294</v>
+        <v>-0.1104</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8277</v>
+        <v>-0.1104</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3016</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2703</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5614</v>
+        <v>-2.3256</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8113</v>
+        <v>-1.501</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7501</v>
+        <v>-0.8246</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7902</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8219</v>
+        <v>-0.5861</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.2272</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7388</v>
+        <v>-0.8133</v>
       </c>
       <c r="V24" t="n">
         <v>0.6991000000000001</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.486999999999999</v>
+        <v>7.176399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>12.0884</v>
+        <v>12.0885</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6014</v>
+        <v>-4.912</v>
       </c>
       <c r="G25" t="n">
-        <v>4.272900000000002</v>
+        <v>4.2729</v>
       </c>
       <c r="H25" t="n">
         <v>6.8956</v>
@@ -2404,13 +2404,13 @@
         <v>13.5154</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.170800000000001</v>
+        <v>-6.4813</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9623000000000004</v>
+        <v>0.9624000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-8.132999999999999</v>
+        <v>-7.4436</v>
       </c>
       <c r="V25" t="n">
         <v>10.3502</v>
@@ -2419,7 +2419,7 @@
         <v>10.9086</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5584</v>
+        <v>-0.5583999999999998</v>
       </c>
     </row>
   </sheetData>
